--- a/stories/arbres/ATOM-FAM.SEC.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est bientôt l'anniversaire de maman. Constance peint un galet. Papa aide. La peinture sent un peu. Papa dit : c'est une surprise gentille. On la garde un peu. Constance pose le galet dans une boîte. La boîte est dans le tiroir. Maman passe. Constance sourit. Elle garde un peu. Puis on dit. Papa dit : maintenant, on révèle. Constance ouvre la boîte. Elle tend le galet. Constance dit : c'est pour toi, maman. Maman rit. Elle touche le galet lisse. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Constance tape des mains. Maman dit merci.</t>
+          <t>C'est bientôt l'anniversaire de maman. Constance peint un galet. Papa aide. La peinture sent un peu. C'est une surprise gentille. On la garde un peu. Constance pose le galet dans une boîte. La boîte est dans le tiroir. Maman passe. Constance sourit. Elle garde un peu. Puis on dit. Maintenant, on révèle. Constance ouvre la boîte. Elle tend le galet. C'est pour toi, maman. Maman rit. Elle touche le galet lisse. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Constance tape des mains. Maman dit merci.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est bientôt l'anniversaire de maman. Constance peint un galet. Papa aide. La peinture sent un peu.
+papa|C'est une surprise gentille. On la garde un peu.
+narrateur|Constance pose le galet dans une boîte. La boîte est dans le tiroir. Maman passe. Constance sourit. Elle garde un peu. Puis on dit.
+papa|Maintenant, on révèle.
+narrateur|Constance ouvre la boîte. Elle tend le galet.
+enfant-f|C'est pour toi, maman. Maman rit. Elle touche le galet lisse. C'était une surprise gentille. On l'a gardée un peu.
+narrateur|Puis on dit. Constance tape des mains. Maman dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Constance cache un galet. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Constance a gardé un peu. Puis on dit. C'était une surprise gentille pour maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman pose le galet sur la table. Constance boit un verre d'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Puis on dit. Constance tape des mains. Maman dit merci.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Constance cache un galet. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Constance a gardé un peu. Puis on dit. C'était une surprise gentille pour maman.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Maman pose le galet sur la table. Constance boit un verre d'eau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.SEC.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La surprise gentille de Constance</t>
+          <t>Le galet soleil de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un galet fait toc dans une poche. Nina le peint en soleil. On le range. Puis on le dit à maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est bientôt l'anniversaire de maman. Constance peint un galet. Papa aide. La peinture sent un peu. C'est une surprise gentille. On la garde un peu. Constance pose le galet dans une boîte. La boîte est dans le tiroir. Maman passe. Constance sourit. Elle garde un peu. Puis on dit. Maintenant, on révèle. Constance ouvre la boîte. Elle tend le galet. C'est pour toi, maman. Maman rit. Elle touche le galet lisse. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Constance tape des mains. Maman dit merci.</t>
+          <t>Un galet rond fait toc dans une poche. Il tape contre un bouton. La poche sent le vent du chemin. Dans la maison, un journal est ouvert. Les pages sont grises et un peu froides. Une goutte de peinture bleue attend. Elle brille comme une petite mare. La fenêtre de l'atelier est embuée. Un rayon passe sur la table de bois. Nina, viens voir le galet. En ce moment, Nina pose le galet. Le galet est gris et lisse. On le peint pour maman. C'est bientôt son anniversaire. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nina prend le pinceau. Les poils sont doux et mouillés. Elle pose du bleu sur le galet. Ça sent un peu la peinture. Papa, c'est joli ? Oui. Bravo, Nina. Tu as fait du bon travail. Maintenant un point jaune. Nina pose le jaune au milieu. Le galet devient un petit soleil. On le laisse sécher un peu. Le soleil peint est encore collant. Nina, on le range ? Oui, papa. Nina pose le galet dans une boîte. La boîte est en carton rêche. Le tiroir va l'attendre. Papa ouvre un tiroir. Le tiroir glisse tout doux. La boîte va dedans. On la garde un peu. Puis on dit. Puis on dit. Bravo. Des pas arrivent dans le couloir. Maman passe près de la porte. Ça sent la peinture ici. Nina a envie de parler. Encore un tout petit peu. Encore un peu. Je reviens tout à l'heure. Le soir, la table sent la soupe. Une petite lumière est allumée. Papa sort la boîte du tiroir. Maintenant, on révèle. Nina ouvre la boîte. Le galet est lisse et froid. Elle le tend vers maman. C'est pour toi, maman. Surprise. C'est un soleil. Il est bleu et jaune. Merci, Nina. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Bravo. Tu as fait du bon travail. Nina tape des mains. Maman touche le galet. Il est tout lisse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1324,75 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est bientôt l'anniversaire de maman. Constance peint un galet. Papa aide. La peinture sent un peu.
-papa|C'est une surprise gentille. On la garde un peu.
-narrateur|Constance pose le galet dans une boîte. La boîte est dans le tiroir. Maman passe. Constance sourit. Elle garde un peu. Puis on dit.
+          <t>narrateur|Un galet rond fait toc dans une poche.
+narrateur|Il tape contre un bouton.
+narrateur|La poche sent le vent du chemin.
+narrateur|Dans la maison, un journal est ouvert.
+narrateur|Les pages sont grises et un peu froides.
+narrateur|Une goutte de peinture bleue attend.
+narrateur|Elle brille comme une petite mare.
+narrateur|La fenêtre de l'atelier est embuée.
+narrateur|Un rayon passe sur la table de bois.
+papa|Nina, viens voir le galet.
+narrateur|En ce moment, Nina pose le galet.
+narrateur|Le galet est gris et lisse.
+papa|On le peint pour maman.
+papa|C'est bientôt son anniversaire.
+papa|C'est une surprise gentille.
+papa|On la garde un peu.
+enfant-f|On la garde un peu.
+narrateur|Nina prend le pinceau.
+narrateur|Les poils sont doux et mouillés.
+narrateur|Elle pose du bleu sur le galet.
+narrateur|Ça sent un peu la peinture.
+enfant-f|Papa, c'est joli ?
+papa|Oui.
+papa|Bravo, Nina.
+papa|Tu as fait du bon travail.
+papa|Maintenant un point jaune.
+narrateur|Nina pose le jaune au milieu.
+narrateur|Le galet devient un petit soleil.
+papa|On le laisse sécher un peu.
+narrateur|Le soleil peint est encore collant.
+papa|Nina, on le range ?
+enfant-f|Oui, papa.
+narrateur|Nina pose le galet dans une boîte.
+narrateur|La boîte est en carton rêche.
+papa|Le tiroir va l'attendre.
+narrateur|Papa ouvre un tiroir.
+narrateur|Le tiroir glisse tout doux.
+narrateur|La boîte va dedans.
+papa|On la garde un peu.
+papa|Puis on dit.
+enfant-f|Puis on dit.
+papa|Bravo.
+narrateur|Des pas arrivent dans le couloir.
+narrateur|Maman passe près de la porte.
+maman|Ça sent la peinture ici.
+narrateur|Nina a envie de parler.
+papa|Encore un tout petit peu.
+enfant-f|Encore un peu.
+maman|Je reviens tout à l'heure.
+narrateur|Le soir, la table sent la soupe.
+narrateur|Une petite lumière est allumée.
+narrateur|Papa sort la boîte du tiroir.
 papa|Maintenant, on révèle.
-narrateur|Constance ouvre la boîte. Elle tend le galet.
-enfant-f|C'est pour toi, maman. Maman rit. Elle touche le galet lisse. C'était une surprise gentille. On l'a gardée un peu.
-narrateur|Puis on dit. Constance tape des mains. Maman dit merci.</t>
+narrateur|Nina ouvre la boîte.
+narrateur|Le galet est lisse et froid.
+narrateur|Elle le tend vers maman.
+enfant-f|C'est pour toi, maman.
+enfant-f|Surprise.
+maman|C'est un soleil.
+enfant-f|Il est bleu et jaune.
+maman|Merci, Nina.
+maman|C'était une surprise gentille.
+papa|On l'a gardée un peu.
+papa|Puis on dit.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Nina tape des mains.
+narrateur|Maman touche le galet.
+enfant-f|Il est tout lisse.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1346,7 +1420,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Constance cache un galet. C'est quoi ?</t>
+          <t>Nina range le galet. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1576,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Constance cache un galet. C'est quoi ?</t>
+          <t>narrateur|Nina range le galet.
+narrateur|C'est quoi ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1605,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Constance a gardé un peu. Puis on dit. C'était une surprise gentille pour maman.</t>
+          <t>Nina a gardé un peu. Puis on dit. C'était une surprise gentille. Tu as rangé le galet ? Oui. Puis tu l'as dit à maman. Bravo, Nina. Le soleil est sur la table. Le carton rêche reste ouvert. La peinture sent encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1749,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Constance a gardé un peu. Puis on dit. C'était une surprise gentille pour maman.</t>
+          <t>narrateur|Nina a gardé un peu.
+narrateur|Puis on dit.
+narrateur|C'était une surprise gentille.
+papa|Tu as rangé le galet ?
+enfant-f|Oui.
+papa|Puis tu l'as dit à maman.
+maman|Bravo, Nina.
+maman|Le soleil est sur la table.
+narrateur|Le carton rêche reste ouvert.
+narrateur|La peinture sent encore un peu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1786,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose le galet sur la table. Constance boit un verre d'eau.</t>
+          <t>Maman pose le galet près de l'assiette. Il va rester avec nous. Tu bois un peu d'eau ? Nina prend le verre. L'eau est fraîche. Le galet brille. Oui. C'est ta surprise gentille. On l'a gardée un peu. Puis on a dit. La petite lumière reste allumée. La soupe fume encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1838,7 +1922,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman pose le galet sur la table. Constance boit un verre d'eau.</t>
+          <t>narrateur|Maman pose le galet près de l'assiette.
+maman|Il va rester avec nous.
+papa|Tu bois un peu d'eau ?
+narrateur|Nina prend le verre.
+narrateur|L'eau est fraîche.
+enfant-f|Le galet brille.
+maman|Oui.
+maman|C'est ta surprise gentille.
+papa|On l'a gardée un peu.
+papa|Puis on a dit.
+narrateur|La petite lumière reste allumée.
+narrateur|La soupe fume encore.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le galet soleil dort près de l'assiette. C'était pour maman. Merci, ma grande. Bravo, Nina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2006,7 +2101,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Le galet soleil dort près de l'assiette.
+enfant-f|C'était pour maman.
+maman|Merci, ma grande.
+papa|Bravo, Nina.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2165,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un galet rond fait toc dans une poche. Il tape contre un bouton. La poche sent le vent du chemin. Dans la maison, un journal est ouvert. Les pages sont grises et un peu froides. Une goutte de peinture bleue attend. Elle brille comme une petite mare. La fenêtre de l'atelier est embuée. Un rayon passe sur la table de bois. Nina, viens voir le galet. En ce moment, Nina pose le galet. Le galet est gris et lisse. On le peint pour maman. C'est bientôt son anniversaire. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nina prend le pinceau. Les poils sont doux et mouillés. Elle pose du bleu sur le galet. Ça sent un peu la peinture. Papa, c'est joli ? Oui. Bravo, Nina. Tu as fait du bon travail. Maintenant un point jaune. Nina pose le jaune au milieu. Le galet devient un petit soleil. On le laisse sécher un peu. Le soleil peint est encore collant. Nina, on le range ? Oui, papa. Nina pose le galet dans une boîte. La boîte est en carton rêche. Le tiroir va l'attendre. Papa ouvre un tiroir. Le tiroir glisse tout doux. La boîte va dedans. On la garde un peu. Puis on dit. Puis on dit. Bravo. Des pas arrivent dans le couloir. Maman passe près de la porte. Ça sent la peinture ici. Nina a envie de parler. Encore un tout petit peu. Encore un peu. Je reviens tout à l'heure. Le soir, la table sent la soupe. Une petite lumière est allumée. Papa sort la boîte du tiroir. Maintenant, on révèle. Nina ouvre la boîte. Le galet est lisse et froid. Elle le tend vers maman. C'est pour toi, maman. Surprise. C'est un soleil. Il est bleu et jaune. Merci, Nina. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Bravo. Tu as fait du bon travail. Nina tape des mains. Maman touche le galet. Il est tout lisse.</t>
+          <t>Un galet rond fait toc dans une poche. Il tape contre un bouton. La poche sent le vent du chemin. Dans la maison, un journal est ouvert. Les pages sont grises et un peu froides. Une goutte de peinture bleue attend. Elle brille comme une petite mare. La fenêtre de l'atelier est embuée. Un rayon passe sur la table de bois. Nina, viens voir le galet. En ce moment, Nina pose le galet. Le galet est gris et lisse. On le peint pour maman. C'est bientôt son anniversaire. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nina prend le pinceau. Les poils sont doux et mouillés. Elle pose du bleu sur le galet. Ça sent un peu la peinture. Papa, c'est joli ? Oui. Bravo, Nina. Maintenant un point jaune. Nina pose le jaune au milieu. Le galet devient un petit soleil. On le laisse sécher un peu. Le soleil peint est encore collant. Nina, on le range ? Oui, papa. Nina pose le galet dans une boîte. La boîte est en carton rêche. Le tiroir va l'attendre. Papa ouvre un tiroir. Le tiroir glisse tout doux. La boîte va dedans. On la garde un peu. Puis on dit. Puis on dit. Bravo. Des pas arrivent dans le couloir. Maman passe près de la porte. Ça sent la peinture ici. Nina a envie de parler. Encore un tout petit peu. Encore un peu. Je reviens tout à l'heure. Le soir, la table sent la soupe. Une petite lumière est allumée. Papa sort la boîte du tiroir. Maintenant, on révèle. Nina ouvre la boîte. Le galet est lisse et froid. Elle le tend vers maman. C'est pour toi, maman. Surprise. C'est un soleil. Il est bleu et jaune. Merci, Nina. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Bravo. Nina tape des mains. Maman touche le galet. Il est tout lisse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;C'est bientôt l'anniversaire de maman. Constance peint un galet. Papa aide. La peinture sent un peu. Papa dit : c'est une &lt;emphasis level="moderate"&gt;surprise&lt;/emphasis&gt; gentille. On la garde un peu. Constance pose le galet dans une boîte. La boîte est dans le tiroir. Maman passe. Constance sourit. Elle garde un peu. Puis on dit. Papa dit : maintenant, on révèle. Constance ouvre la boîte. Elle tend le galet. Constance dit : c'est pour toi, maman. Maman rit. Elle touche le galet lisse. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Constance tape des mains. Maman dit merci.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un galet rond fait toc dans une poche. Il tape contre un bouton. La poche sent le vent du chemin. Dans la maison, un journal est ouvert. Les pages sont grises et un peu froides. Une goutte de peinture bleue attend. Elle brille comme une petite mare. La fenêtre de l'atelier est embuée. Un rayon passe sur la table de bois. Nina, viens voir le galet. En ce moment, Nina pose le galet. Le galet est gris et lisse. On le peint pour maman. C'est bientôt son anniversaire. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nina prend le pinceau. Les poils sont doux et mouillés. Elle pose du bleu sur le galet. Ça sent un peu la peinture. Papa, c'est joli ? Oui. Bravo, Nina. Maintenant un point jaune. Nina pose le jaune au milieu. Le galet devient un petit soleil. On le laisse sécher un peu. Le soleil peint est encore collant. Nina, on le range ? Oui, papa. Nina pose le galet dans une boîte. La boîte est en carton rêche. Le tiroir va l'attendre. Papa ouvre un tiroir. Le tiroir glisse tout doux. La boîte va dedans. On la garde un peu. Puis on dit. Puis on dit. Bravo. Des pas arrivent dans le couloir. Maman passe près de la porte. Ça sent la peinture ici. Nina a envie de parler. Encore un tout petit peu. Encore un peu. Je reviens tout à l'heure. Le soir, la table sent la soupe. Une petite lumière est allumée. Papa sort la boîte du tiroir. Maintenant, on révèle. Nina ouvre la boîte. Le galet est lisse et froid. Elle le tend vers maman. C'est pour toi, maman. Surprise. C'est un soleil. Il est bleu et jaune. Merci, Nina. C'était une surprise gentille. On l'a gardée un peu. Puis on dit. Bravo. Nina tape des mains. Maman touche le galet. Il est tout lisse.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1348,7 +1348,6 @@
 enfant-f|Papa, c'est joli ?
 papa|Oui.
 papa|Bravo, Nina.
-papa|Tu as fait du bon travail.
 papa|Maintenant un point jaune.
 narrateur|Nina pose le jaune au milieu.
 narrateur|Le galet devient un petit soleil.
@@ -1389,13 +1388,11 @@
 papa|On l'a gardée un peu.
 papa|Puis on dit.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 narrateur|Nina tape des mains.
 narrateur|Maman touche le galet.
 enfant-f|Il est tout lisse.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1425,7 +1422,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Constance cache un galet. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina range le galet. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1580,7 +1577,6 @@
 narrateur|C'est quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1610,7 +1606,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Constance a gardé un peu. Puis on dit. C'était une &lt;emphasis level="moderate"&gt;surprise&lt;/emphasis&gt; gentille pour maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a gardé un peu. Puis on dit. C'était une surprise gentille. Tu as rangé le galet ? Oui. Puis tu l'as dit à maman. Bravo, Nina. Le soleil est sur la table. Le carton rêche reste ouvert. La peinture sent encore un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1761,7 +1757,6 @@
 narrateur|La peinture sent encore un peu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman pose le galet sur la table. Constance boit un verre d'eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman pose le galet près de l'assiette. Il va rester avec nous. Tu bois un peu d'eau ? Nina prend le verre. L'eau est fraîche. Le galet brille. Oui. C'est ta surprise gentille. On l'a gardée un peu. Puis on a dit. La petite lumière reste allumée. La soupe fume encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1936,7 +1931,6 @@
 narrateur|La soupe fume encore.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le galet soleil dort près de l'assiette. C'était pour maman. Merci, ma grande. Bravo, Nina. L'histoire est finie.</t>
+          <t>Le galet soleil dort près de l'assiette. C'était pour maman. Merci, ma grande. Bravo, Nina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le galet soleil dort près de l'assiette. C'était pour maman. Merci, ma grande. Bravo, Nina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2104,11 +2098,9 @@
           <t>narrateur|Le galet soleil dort près de l'assiette.
 enfant-f|C'était pour maman.
 maman|Merci, ma grande.
-papa|Bravo, Nina.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Nina.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2127,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2172,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Constance, papa, maman</t>
+          <t>Nina, papa, maman</t>
         </is>
       </c>
     </row>
